--- a/docs/assumptions_and_decision_log_template.xlsx
+++ b/docs/assumptions_and_decision_log_template.xlsx
@@ -1,30 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <fileSharing readOnlyRecommended="1"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2251B87-AA97-4944-972F-4A3492BE64EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{62AF8086-0EBD-4C11-BCC3-491AAB208AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="720" windowWidth="26310" windowHeight="14295" tabRatio="856" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="856" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Introduction" sheetId="11" r:id="rId1"/>
-    <sheet name="Analysis Overview" sheetId="9" r:id="rId2"/>
-    <sheet name="Analysis Map" sheetId="15" r:id="rId3"/>
-    <sheet name="Roles and Responsibilities" sheetId="10" r:id="rId4"/>
-    <sheet name="R&amp;R Resources" sheetId="12" r:id="rId5"/>
-    <sheet name="QA Log" sheetId="14" r:id="rId6"/>
-    <sheet name="Decisions &amp; Issues Logs" sheetId="7" r:id="rId7"/>
-    <sheet name="Assumptions log " sheetId="6" r:id="rId8"/>
-    <sheet name="Quality &amp; Sensitivity Guide" sheetId="5" r:id="rId9"/>
-    <sheet name="Ethics Log" sheetId="13" r:id="rId10"/>
-    <sheet name="Risk Scoring Guide" sheetId="8" r:id="rId11"/>
-    <sheet name="ranges" sheetId="16" r:id="rId12"/>
+    <sheet name="README" sheetId="17" r:id="rId1"/>
+    <sheet name="Introduction" sheetId="11" r:id="rId2"/>
+    <sheet name="Analysis Overview" sheetId="9" r:id="rId3"/>
+    <sheet name="Analysis Map" sheetId="15" r:id="rId4"/>
+    <sheet name="Roles and Responsibilities" sheetId="10" r:id="rId5"/>
+    <sheet name="R&amp;R Resources" sheetId="12" r:id="rId6"/>
+    <sheet name="QA Log" sheetId="14" r:id="rId7"/>
+    <sheet name="Decisions &amp; Issues Logs" sheetId="7" r:id="rId8"/>
+    <sheet name="Assumptions log " sheetId="6" r:id="rId9"/>
+    <sheet name="Quality &amp; Sensitivity Guide" sheetId="5" r:id="rId10"/>
+    <sheet name="Ethics Log" sheetId="13" r:id="rId11"/>
+    <sheet name="Risk Scoring Guide" sheetId="8" r:id="rId12"/>
+    <sheet name="ranges" sheetId="16" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Decisions &amp; Issues Logs'!$B$40:$L$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Roles and Responsibilities'!$B$10:$J$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Decisions &amp; Issues Logs'!$B$40:$L$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Roles and Responsibilities'!$B$10:$J$11</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -101,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="243">
   <si>
     <t>While most of the template should be self explanatory, this introductory slide sets out basic guidance on use.</t>
   </si>
@@ -143,9 +144,6 @@
   </si>
   <si>
     <t>A table which allows the Analytical Assurer to document planned Quality Assurance and confirm when it is completed. Also has space for a short summary of the issues the Quality Assurance raised. This information should be described more fully in the decisions and issues register</t>
-  </si>
-  <si>
-    <t>Decisions &amp; Issues Register</t>
   </si>
   <si>
     <t>Assumptions Log</t>
@@ -343,10 +341,6 @@
     <t>Roles and responsibilties for [Insert Analysis Name &amp; Financial Year of Interest]</t>
   </si>
   <si>
-    <t>This sheet records which individuals serve in which role. 
-When there is a handover, the new name must be added to a separate table with the date of handover clearly recorded.</t>
-  </si>
-  <si>
     <t>Role</t>
   </si>
   <si>
@@ -374,13 +368,7 @@
     <t>Next review/update due on</t>
   </si>
   <si>
-    <t>Senior Responsible Owner</t>
-  </si>
-  <si>
     <t>Commissioner</t>
-  </si>
-  <si>
-    <t>Analytical Assurer</t>
   </si>
   <si>
     <t xml:space="preserve">Handover Example </t>
@@ -414,12 +402,6 @@
     <t>Commissioner Overview</t>
   </si>
   <si>
-    <t>Analytical Assurer Overview</t>
-  </si>
-  <si>
-    <t>Analytical Assurer Responsibilites</t>
-  </si>
-  <si>
     <t>Responsibility</t>
   </si>
   <si>
@@ -438,9 +420,6 @@
     <t>I agree to ensure that sufficent quality assurance happens throughout analysis development and that the analysis complies with the ONS Quality Standard for Analysis</t>
   </si>
   <si>
-    <t>I agree to ensure a high level of understanding of the requirements, scope and context of the analysis, not just for myself, but for the SRO, the Analytical Assurer and the Analyst(s)</t>
-  </si>
-  <si>
     <t>I agree to understand and keep up to date with the the strengths, limitations and contexts of the analysis</t>
   </si>
   <si>
@@ -450,22 +429,10 @@
     <t>I agree to transmit information regarding user needs from end users to the analysis team, ensuring that the analysis is developed according to user needs</t>
   </si>
   <si>
-    <t>Commissioner Documents</t>
-  </si>
-  <si>
-    <t>Analytical Assurer Documents</t>
-  </si>
-  <si>
-    <t>Name &amp; Description</t>
-  </si>
-  <si>
     <t>Created by</t>
   </si>
   <si>
     <t xml:space="preserve">Name &amp; Description </t>
-  </si>
-  <si>
-    <t>TODO: Create Word Template</t>
   </si>
   <si>
     <t>QA Plan &amp; Log for [Insert Analysis Name &amp; Financial Year of Interest]</t>
@@ -670,9 +637,6 @@
   </si>
   <si>
     <t>https://uksa.statisticsauthority.gov.uk/the-authority-board/committees/national-statisticians-advisory-committees-and-panels/national-statisticians-data-ethics-advisory-committee/ethics-self-assessment-tool/</t>
-  </si>
-  <si>
-    <t>When you have completed the ethics log, copy-paste the results into this tab to ensure the log is stored correctly with all other documentation</t>
   </si>
   <si>
     <t xml:space="preserve">The riskiest assumptions and decisions are those with low evidence quality and high impact on final results. </t>
@@ -765,46 +729,13 @@
     <t>Most teams create process maps or model maps during development. These are very helpful to give an overview of the analysis workflow.</t>
   </si>
   <si>
-    <t>The commissioner:
-requests the analysis and sets out their requirements
-agrees that what the analyst is going to do will satisfy the need
-accepts the analysis and assurance as fit for purpose</t>
-  </si>
-  <si>
-    <t>The analytical assurer:
-reviews the assurance completed by the analyst
-carries out any further validation and verification they may see as appropriate
-reports errors and areas for improvement to the analyst
-undertakes repeated reviews as required
-confirms the work has been appropriately scoped, executed, validated and verified and documented to the approver
-can be a group of assurers, in which case the leader of the group is responsible
-must be independent from the analysts</t>
-  </si>
-  <si>
     <t>I agree to ensure that quality assurance is appropriately varied, including code review, documentation review, methodological review and discussion with the analysis team when required to ensure development occurs as planned.</t>
   </si>
   <si>
-    <t>I will ensure that the feedback given by the Quality Assurers is fully documented and reviewed by the analysts</t>
-  </si>
-  <si>
     <t>I agree to ensure that relevant limitations, uncertainties and caveats detected by quality assurance are communicated to end users appropriately by the analytical team.</t>
   </si>
   <si>
     <t>I agree to transmit information regarding the strengths, limitations, context and uncertainties from the analytical team to end users as appropriate to ensure appropriate analysis development.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Commissioning document: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Sets out the question the analysis tries to answer and how this analysis will try to answer it. 
-The commissioning document must be completed before production begins. It should be created in collaboration with end users and the analytical team. The document must set out broad specifications for the analysis including accuracy requirements, delivery timeline and skill gaps that must be addressed before completion.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -822,18 +753,7 @@
     </r>
   </si>
   <si>
-    <t>Approver (Senior Responsible Owner) overview</t>
-  </si>
-  <si>
-    <t>The approver (may be known as senior analyst or senior responsible officer):
-scrutinises the work of the analyst and assurer
-confirms (if necessary) to the analyst, assurer and commissioner that the work has been appropriately assured</t>
-  </si>
-  <si>
     <t>Approver (SRO)</t>
-  </si>
-  <si>
-    <t>Approver Documents</t>
   </si>
   <si>
     <t>I agree to ensure tha key risks, limitations, major assumptions of the analysis and uncertainty associated with the outcomes are communicated appropriately to users</t>
@@ -868,22 +788,10 @@
     <t>Analyst Overview</t>
   </si>
   <si>
-    <t>The analyst:
-designs the approach, including the assurance, to meet the commissioner’s requirements
-agrees the approach with the commissioner
-carries out the analysis
-carries out their own assurance
-acts on findings from the assurer
-can be a group of analysts, in which case the lead analyst is responsible</t>
-  </si>
-  <si>
     <t>I agree to set up sufficent quality assurance throughout the analysis and to ensure that the analysis complies with the ONS Quality Standard for Analysis</t>
   </si>
   <si>
     <t>I agree to ensure that the analysis is appropriately documented in line with the ONS Quality Standard for Analysis.</t>
-  </si>
-  <si>
-    <t>I will ensure that the feedback given by the Quality Assurers is fully considered and taken on board by the analyst team</t>
   </si>
   <si>
     <t>I agree to ensure that relevant assumptions, limitations, uncertainties and caveats are communicated to end users appropriately by the analytical team.</t>
@@ -984,12 +892,121 @@
   <si>
     <t>Analyst</t>
   </si>
+  <si>
+    <t>Assurer</t>
+  </si>
+  <si>
+    <t>Approver (also known as Senior Responsible Owner)</t>
+  </si>
+  <si>
+    <t>This sheet records which individuals serve in which role. Create new lines if more than one person has the same role. 
+When there is a handover, the new name must be added to a separate table with the date of handover clearly recorded.</t>
+  </si>
+  <si>
+    <t>Assurer Overview</t>
+  </si>
+  <si>
+    <t>Assurer Documents</t>
+  </si>
+  <si>
+    <t>Assurer Responsibilites</t>
+  </si>
+  <si>
+    <t>The assurer:
+* reviews the assurance completed by the analyst
+* carries out any further validation and verification they may see as appropriate
+* reports errors and areas for improvement to the analyst
+* undertakes repeated reviews as required
+* confirms the work has been appropriately scoped, executed, validated and verified and documented to the approver
+* can be a group of assurers, in which case the leader of the group is responsible
+* must be independent from the analysts</t>
+  </si>
+  <si>
+    <t>The commissioner:
+* requests the analysis and sets out their requirements
+* agrees that what the analyst is going to do will satisfy the need
+* accepts the analysis and assurance as fit for purpose</t>
+  </si>
+  <si>
+    <t>The analyst:
+* designs the approach, including the assurance, to meet the commissioner’s requirements
+* agrees the approach with the commissioner
+* carries out the analysis
+* carries out their own assurance
+* acts on findings from the assurer
+* can be a group of analysts, in which case the lead analyst is responsible</t>
+  </si>
+  <si>
+    <t>The approver (may be known as senior analyst or senior responsible owner/officer):
+* scrutinises the work of the analyst and assurer
+* confirms (if necessary) to the analyst, assurer and commissioner that the work has been appropriately assured</t>
+  </si>
+  <si>
+    <t>Approver overview</t>
+  </si>
+  <si>
+    <t>I agree to ensure a high level of understanding of the requirements, scope and context of the analysis, not just for myself, but for the Approver, the Assurer and the Analyst(s)</t>
+  </si>
+  <si>
+    <t>I will ensure that the feedback given by the Assurer(s) is fully documented and reviewed by the analysts</t>
+  </si>
+  <si>
+    <t>I will ensure that the feedback given by the Assurers is fully considered and taken on board by the analyst team</t>
+  </si>
+  <si>
+    <t>Version #</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Editor</t>
+  </si>
+  <si>
+    <t>Alpha version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This Excel workbook has been developed and is maintained by the Analysis Standards and Pipelines Hub, based in Quality and Improvement Division at ONS. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternatively, you can email ASAP@ons.gov.uk </t>
+  </si>
+  <si>
+    <t>ASAP</t>
+  </si>
+  <si>
+    <t>Pre March 2026</t>
+  </si>
+  <si>
+    <t>Updated for new AQUA book roles</t>
+  </si>
+  <si>
+    <t>Assumptions and decision log template</t>
+  </si>
+  <si>
+    <t>This template is an ALPHA draft. It is in development and we are still working to ensure that it meets user needs.</t>
+  </si>
+  <si>
+    <t>This workbook supports analysis development and production by providing a structured template for documentation.</t>
+  </si>
+  <si>
+    <t>Decisions &amp; Issues Logs</t>
+  </si>
+  <si>
+    <t>Ethics Log</t>
+  </si>
+  <si>
+    <t>When you have completed the ethics log, link (or copy-paste) the results into this tab to ensure the log is stored correctly with all other documentation</t>
+  </si>
+  <si>
+    <t>Ethical issues relating to the analysis documented</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1211,8 +1228,28 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1276,6 +1313,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6E0B4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2CEEF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E6A2"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -1655,7 +1704,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1793,9 +1842,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1860,9 +1906,6 @@
     <xf numFmtId="0" fontId="21" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2018,6 +2061,51 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="34" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="15" fontId="34" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2910,153 +2998,243 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE0E718D-ABA6-478B-BFB8-19647D312746}">
-  <dimension ref="B2:D22"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AAA8E9D-25BB-4C3E-B39D-B9279D375DDF}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="43"/>
-    <col min="2" max="2" width="15.7109375" style="75" customWidth="1"/>
-    <col min="3" max="3" width="94.28515625" style="50" customWidth="1"/>
-    <col min="4" max="4" width="39" style="43" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="43"/>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="76.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="89" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="89" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="89" t="s">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="149" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="149"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="149"/>
+    </row>
+    <row r="2" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="152" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="89" t="s">
+      <c r="B2" s="149"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="149"/>
+    </row>
+    <row r="3" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="149" t="s">
+        <v>232</v>
+      </c>
+      <c r="B3" s="149"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="149"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="153"/>
+      <c r="B4" s="150"/>
+      <c r="C4" s="154"/>
+      <c r="D4" s="150"/>
+    </row>
+    <row r="5" spans="1:4" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A5" s="155" t="s">
+        <v>236</v>
+      </c>
+      <c r="B5" s="150"/>
+      <c r="C5" s="150"/>
+      <c r="D5" s="150"/>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="150"/>
+      <c r="B6" s="150"/>
+      <c r="C6" s="150"/>
+      <c r="D6" s="150"/>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="156" t="s">
+        <v>227</v>
+      </c>
+      <c r="B7" s="156" t="s">
+        <v>228</v>
+      </c>
+      <c r="C7" s="156" t="s">
+        <v>229</v>
+      </c>
+      <c r="D7" s="156" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="163">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8" s="164" t="s">
+        <v>235</v>
+      </c>
+      <c r="C8" s="163" t="s">
+        <v>233</v>
+      </c>
+      <c r="D8" s="165">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="157">
+        <v>1</v>
+      </c>
+      <c r="B9" s="159" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="157" t="s">
+        <v>233</v>
+      </c>
+      <c r="D9" s="158" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="150"/>
+      <c r="B10" s="154"/>
+      <c r="C10" s="150"/>
+      <c r="D10" s="150"/>
+    </row>
+    <row r="11" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="150"/>
+      <c r="B11" s="160" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="150"/>
+      <c r="D11" s="150"/>
+    </row>
+    <row r="12" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="150"/>
+      <c r="B12" s="161" t="s">
+        <v>238</v>
+      </c>
+      <c r="C12" s="150"/>
+      <c r="D12" s="150"/>
+    </row>
+    <row r="13" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="150"/>
+      <c r="B13" s="162" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="54" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="54" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B8" s="54" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="74" t="s">
-        <v>185</v>
-      </c>
-      <c r="D8" s="74"/>
-    </row>
-    <row r="9" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B9" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="74" t="s">
-        <v>186</v>
-      </c>
-      <c r="D9" s="74"/>
-    </row>
-    <row r="10" spans="2:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B10" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="74" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="74" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="54" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="74"/>
-    </row>
-    <row r="12" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B12" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="74"/>
-    </row>
-    <row r="13" spans="2:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="B13" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="103" t="s">
-        <v>188</v>
-      </c>
-      <c r="D13" s="76"/>
-    </row>
-    <row r="14" spans="2:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="B14" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="104" t="s">
-        <v>189</v>
-      </c>
-      <c r="D14" s="74"/>
-    </row>
-    <row r="15" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B15" s="54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="74" t="s">
-        <v>190</v>
-      </c>
-      <c r="D15" s="74"/>
-    </row>
-    <row r="16" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B16" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="74"/>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C17" s="75"/>
-      <c r="D17" s="75"/>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="D19" s="50"/>
-    </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="D20" s="50"/>
-    </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="D21" s="50"/>
-    </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="D22" s="50"/>
+      <c r="C13" s="150"/>
+      <c r="D13" s="150"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://best-practice-and-impact.github.io/analysis_project_documentation/" xr:uid="{452EC8AD-EA22-413A-AC1F-45EACD99AA16}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="40.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="37.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="34.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="42.85546875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" spans="1:8" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="185" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2" s="93" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F2" s="188" t="s">
+        <v>207</v>
+      </c>
+      <c r="G2" s="94" t="s">
+        <v>149</v>
+      </c>
+      <c r="H2" s="76" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="144.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="186"/>
+      <c r="C3" s="92" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="146" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="188"/>
+      <c r="G3" s="94" t="s">
+        <v>153</v>
+      </c>
+      <c r="H3" s="76" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="187"/>
+      <c r="C4" s="91" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F4" s="188"/>
+      <c r="G4" s="94" t="s">
+        <v>148</v>
+      </c>
+      <c r="H4" s="76" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="F7" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="F2:F4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;K000000 OFFICIAL-FOR PUBLIC RELEASE&amp;1#_x000D_</oddHeader>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;K000000 OFFICIAL-FOR PUBLIC RELEASE</oddFooter>
@@ -3064,7 +3242,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470DF315-86F2-4A76-BD43-D9F1F2DB47B8}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -3074,22 +3252,22 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="78" t="s">
-        <v>170</v>
+      <c r="B3" s="77" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>171</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -3104,7 +3282,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E243E638-BE3D-4BC2-9B58-98933D2F1E85}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -3122,22 +3300,22 @@
   <sheetData>
     <row r="2" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B2" s="23" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="23" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D6" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3146,7 +3324,7 @@
       <c r="F7" s="33"/>
       <c r="G7" s="33"/>
       <c r="H7" s="34" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="I7" s="33"/>
       <c r="J7" s="30"/>
@@ -3158,63 +3336,63 @@
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D9" s="36"/>
       <c r="G9" s="27" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="J9" s="24"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D10" s="36"/>
       <c r="F10" s="26" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="I10" s="31" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="J10" s="24"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D11" s="37" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="I11" s="31" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="J11" s="24"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D12" s="36"/>
       <c r="F12" s="26" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="I12" s="31" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="J12" s="24"/>
     </row>
@@ -3229,17 +3407,17 @@
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -3251,34 +3429,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD37784D-8874-4633-809D-8C39DC5AF32E}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="109" t="s">
-        <v>180</v>
+      <c r="A3" s="107" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3291,6 +3469,170 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE0E718D-ABA6-478B-BFB8-19647D312746}">
+  <dimension ref="B2:D23"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="43"/>
+    <col min="2" max="2" width="15.7109375" style="74" customWidth="1"/>
+    <col min="3" max="3" width="94.28515625" style="50" customWidth="1"/>
+    <col min="4" max="4" width="39" style="43" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="43"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="88" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="88" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="88" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="88" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B8" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="73" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="73"/>
+    </row>
+    <row r="9" spans="2:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B9" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" s="73"/>
+    </row>
+    <row r="10" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="B10" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="73" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="73"/>
+    </row>
+    <row r="12" spans="2:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B12" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="73" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="73"/>
+    </row>
+    <row r="13" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="B13" s="52" t="s">
+        <v>239</v>
+      </c>
+      <c r="C13" s="101" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="75"/>
+    </row>
+    <row r="14" spans="2:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="B14" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="102" t="s">
+        <v>177</v>
+      </c>
+      <c r="D14" s="73"/>
+    </row>
+    <row r="15" spans="2:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B15" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="73" t="s">
+        <v>178</v>
+      </c>
+      <c r="D15" s="73"/>
+    </row>
+    <row r="16" spans="2:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="54" t="s">
+        <v>240</v>
+      </c>
+      <c r="C16" s="73" t="s">
+        <v>242</v>
+      </c>
+      <c r="D16" s="73"/>
+    </row>
+    <row r="17" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="73" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="73"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="74"/>
+      <c r="D18" s="74"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D20" s="50"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D21" s="50"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D22" s="50"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D23" s="50"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;K000000 OFFICIAL-FOR PUBLIC RELEASE&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;K000000 OFFICIAL-FOR PUBLIC RELEASE</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBE6D9BE-54B5-4C12-A6AF-9C1FCB47261E}">
   <sheetPr>
     <tabColor rgb="FF4472C4"/>
@@ -3307,157 +3649,157 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="44" t="s">
         <v>19</v>
-      </c>
-      <c r="D1" s="44" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B2" s="52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="47"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="48"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" s="53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="48"/>
     </row>
     <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B5" s="53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="48"/>
       <c r="D5" s="50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" s="54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="46"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B9" s="52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="47"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" s="54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="45"/>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B11" s="55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="49"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="B14" s="54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="46"/>
       <c r="D15" s="56" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B16" s="54" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="46"/>
       <c r="D16" s="56" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
       <c r="B19" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="48"/>
+      <c r="D19" s="87" t="s">
         <v>37</v>
-      </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="88" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="44"/>
       <c r="B20" s="52" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" s="48"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B21" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="46"/>
+      <c r="D21" s="87" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D22" s="87" t="s">
         <v>40</v>
-      </c>
-      <c r="C21" s="46"/>
-      <c r="D21" s="88" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D22" s="88" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23" s="51"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B24" s="54" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" s="46"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B25" s="52" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" s="48"/>
     </row>
     <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B26" s="54" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" s="46"/>
     </row>
@@ -3475,7 +3817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B00483A1-29ED-47E5-AD0D-DCC9EB5BD37B}">
   <sheetPr>
     <tabColor rgb="FF4472C4"/>
@@ -3484,7 +3826,7 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="43"/>
-    <col min="2" max="2" width="27.140625" style="72" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" style="71" customWidth="1"/>
     <col min="3" max="3" width="13.5703125" style="43" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" style="43" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" style="43" customWidth="1"/>
@@ -3495,204 +3837,204 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="71"/>
-    </row>
-    <row r="2" spans="1:8" s="70" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69"/>
-      <c r="B2" s="79" t="s">
-        <v>194</v>
-      </c>
-      <c r="D2" s="69"/>
-      <c r="F2" s="73"/>
+      <c r="A1" s="70"/>
+    </row>
+    <row r="2" spans="1:8" s="69" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="68"/>
+      <c r="B2" s="78" t="s">
+        <v>182</v>
+      </c>
+      <c r="D2" s="68"/>
+      <c r="F2" s="72"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="78" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="78" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="79" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="80" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="81" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="43" t="s">
+    </row>
+    <row r="8" spans="1:8" s="68" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="51" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" s="69" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="51" t="s">
+      <c r="D8" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="69" t="s">
+      <c r="F8" s="79" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="80" t="s">
+      <c r="H8" s="68" t="s">
         <v>53</v>
-      </c>
-      <c r="H8" s="69" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="44"/>
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="84" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="43"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="43"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="83" t="s">
+      <c r="D11" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="43" t="s">
+      <c r="F11" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="43" t="s">
+      <c r="H11" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="87" t="s">
+    </row>
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="83" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="84" t="s">
+      <c r="D12" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="F12" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="43" t="s">
+      <c r="H12" s="85" t="s">
         <v>62</v>
       </c>
-      <c r="H12" s="86" t="s">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="80"/>
+      <c r="F13" s="43"/>
+      <c r="H13" s="85" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="81"/>
-      <c r="F13" s="43"/>
-      <c r="H13" s="86" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="80"/>
+      <c r="F14" s="43"/>
+      <c r="H14" s="85" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="81"/>
-      <c r="F14" s="43"/>
-      <c r="H14" s="86" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="44"/>
-      <c r="B15" s="85" t="s">
+      <c r="B15" s="84" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="43"/>
+      <c r="H15" s="85"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="43"/>
-      <c r="H15" s="86"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="83" t="s">
+      <c r="D16" s="81"/>
+      <c r="F16" s="43"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="82"/>
-      <c r="F16" s="43"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" s="82"/>
+      <c r="D17" s="81"/>
       <c r="F17" s="43"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="81"/>
-      <c r="D18" s="82"/>
+      <c r="B18" s="80"/>
+      <c r="D18" s="81"/>
       <c r="F18" s="43"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="81"/>
+      <c r="B19" s="80"/>
       <c r="F19" s="43"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="81"/>
+      <c r="B20" s="80"/>
       <c r="F20" s="43"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="81" t="s">
+      <c r="F21" s="43"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="F21" s="43"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="81" t="s">
-        <v>71</v>
-      </c>
       <c r="F22" s="43"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="81"/>
+      <c r="B23" s="80"/>
       <c r="F23" s="43"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="44"/>
-      <c r="B24" s="81"/>
+      <c r="B24" s="80"/>
       <c r="F24" s="43"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="81"/>
+      <c r="B25" s="80"/>
       <c r="F25" s="43"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="81"/>
+      <c r="B26" s="80"/>
       <c r="F26" s="43"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="81"/>
+      <c r="B27" s="80"/>
       <c r="F27" s="43"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="81"/>
+      <c r="B28" s="80"/>
       <c r="F28" s="43"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="81"/>
+      <c r="B29" s="80"/>
       <c r="F29" s="43"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="81"/>
+      <c r="B30" s="80"/>
       <c r="F30" s="43"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="81"/>
+      <c r="B31" s="80"/>
       <c r="F31" s="43"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="81"/>
+      <c r="B32" s="80"/>
       <c r="F32" s="43"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="81"/>
+      <c r="B33" s="80"/>
       <c r="F33" s="43"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="81"/>
+      <c r="B34" s="80"/>
       <c r="F34" s="43"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B35" s="81"/>
+      <c r="B35" s="80"/>
       <c r="F35" s="43"/>
     </row>
   </sheetData>
@@ -3705,7 +4047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12842DA-5717-4F1A-9C27-596A9E87F6C2}">
   <sheetPr>
     <tabColor theme="7"/>
@@ -3714,7 +4056,7 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="24.42578125" style="40" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" style="40" customWidth="1"/>
     <col min="3" max="4" width="16.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="49.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="44.7109375" style="1" customWidth="1"/>
@@ -3734,7 +4076,7 @@
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="6"/>
@@ -3760,14 +4102,14 @@
     </row>
     <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
-      <c r="B4" s="149" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="150"/>
-      <c r="D4" s="150"/>
-      <c r="E4" s="150"/>
-      <c r="F4" s="150"/>
-      <c r="G4" s="150"/>
+      <c r="B4" s="166" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="167"/>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
       <c r="J4" s="13"/>
@@ -3775,12 +4117,12 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
-      <c r="B5" s="151"/>
-      <c r="C5" s="152"/>
-      <c r="D5" s="152"/>
-      <c r="E5" s="152"/>
-      <c r="F5" s="152"/>
-      <c r="G5" s="152"/>
+      <c r="B5" s="168"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="169"/>
       <c r="H5" s="13"/>
       <c r="I5" s="13"/>
       <c r="J5" s="13"/>
@@ -3788,12 +4130,12 @@
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
-      <c r="B6" s="151"/>
-      <c r="C6" s="152"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
+      <c r="B6" s="168"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="169"/>
+      <c r="F6" s="169"/>
+      <c r="G6" s="169"/>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
@@ -3801,12 +4143,12 @@
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
-      <c r="B7" s="153"/>
-      <c r="C7" s="154"/>
-      <c r="D7" s="154"/>
-      <c r="E7" s="154"/>
-      <c r="F7" s="154"/>
-      <c r="G7" s="154"/>
+      <c r="B7" s="170"/>
+      <c r="C7" s="171"/>
+      <c r="D7" s="171"/>
+      <c r="E7" s="171"/>
+      <c r="F7" s="171"/>
+      <c r="G7" s="171"/>
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
@@ -3832,37 +4174,37 @@
     </row>
     <row r="10" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="E10" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="F10" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="G10" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="H10" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="I10" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="J10" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="I10" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
-      <c r="B11" s="41" t="s">
-        <v>83</v>
+      <c r="B11" s="147" t="s">
+        <v>214</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -3877,7 +4219,7 @@
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="41" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -3891,7 +4233,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" s="42" t="s">
-        <v>85</v>
+        <v>213</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -3904,7 +4246,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" s="42" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -3920,12 +4262,12 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="40" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B17" s="41" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B17" s="147" t="s">
+        <v>214</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -3938,7 +4280,7 @@
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="41" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -3951,7 +4293,7 @@
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="42" t="s">
-        <v>85</v>
+        <v>213</v>
       </c>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -3964,7 +4306,7 @@
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="42" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -3993,7 +4335,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E87623CC-BDB5-445F-9888-FB20932DA010}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -4014,279 +4356,262 @@
     <col min="13" max="13" width="14.42578125" style="60" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="9.140625" style="60"/>
     <col min="16" max="16" width="24.85546875" style="60" customWidth="1"/>
-    <col min="17" max="17" width="56.7109375" style="60" customWidth="1"/>
+    <col min="17" max="17" width="79.85546875" style="60" customWidth="1"/>
     <col min="18" max="18" width="14" style="60" customWidth="1"/>
     <col min="19" max="16384" width="9.140625" style="60"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="59" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="61" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="116" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="139.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="112" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4" s="110" t="s">
+        <v>222</v>
+      </c>
+      <c r="F4" s="109" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="110" t="s">
+        <v>220</v>
+      </c>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="108" t="s">
+        <v>216</v>
+      </c>
+      <c r="L4" s="89" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="114" t="s">
-        <v>203</v>
-      </c>
-      <c r="B4" s="112" t="s">
-        <v>204</v>
-      </c>
-      <c r="F4" s="111" t="s">
-        <v>89</v>
-      </c>
-      <c r="G4" s="112" t="s">
-        <v>195</v>
-      </c>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="110" t="s">
-        <v>90</v>
-      </c>
-      <c r="L4" s="90" t="s">
-        <v>196</v>
-      </c>
-      <c r="P4" s="115" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q4" s="116" t="s">
-        <v>214</v>
+      <c r="P4" s="113" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q4" s="114" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="67" t="s">
-        <v>205</v>
-      </c>
-      <c r="F5" s="128" t="s">
-        <v>221</v>
+      <c r="A5" s="66" t="s">
+        <v>187</v>
+      </c>
+      <c r="F5" s="126" t="s">
+        <v>200</v>
       </c>
       <c r="G5" s="63"/>
       <c r="K5" s="62" t="s">
-        <v>91</v>
-      </c>
-      <c r="P5" s="117" t="s">
-        <v>212</v>
+        <v>218</v>
+      </c>
+      <c r="P5" s="115" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:19" s="62" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="B6" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="M6" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="N6" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q6" s="120" t="s">
+        <v>86</v>
+      </c>
+      <c r="R6" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="S6" s="64" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B7" s="123" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="G7" s="117" t="s">
+        <v>90</v>
+      </c>
+      <c r="H7" s="65"/>
+      <c r="I7" s="65"/>
+      <c r="L7" s="117" t="s">
+        <v>91</v>
+      </c>
+      <c r="M7" s="65"/>
+      <c r="N7" s="65"/>
+      <c r="Q7" s="122" t="s">
+        <v>199</v>
+      </c>
+      <c r="R7" s="119"/>
+      <c r="S7" s="65"/>
+    </row>
+    <row r="8" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B8" s="123" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="65"/>
+      <c r="D8" s="65"/>
+      <c r="G8" s="118" t="s">
+        <v>224</v>
+      </c>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
+      <c r="L8" s="117" t="s">
+        <v>183</v>
+      </c>
+      <c r="M8" s="65"/>
+      <c r="N8" s="65"/>
+      <c r="Q8" s="121" t="s">
+        <v>195</v>
+      </c>
+      <c r="R8" s="65"/>
+      <c r="S8" s="65"/>
+    </row>
+    <row r="9" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B9" s="123" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="G9" s="117" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="L9" s="118" t="s">
+        <v>225</v>
+      </c>
+      <c r="M9" s="65"/>
+      <c r="N9" s="65"/>
+      <c r="Q9" s="90" t="s">
+        <v>196</v>
+      </c>
+      <c r="R9" s="65"/>
+      <c r="S9" s="65"/>
+    </row>
+    <row r="10" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B10" s="123" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65"/>
+      <c r="G10" s="117" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="64" t="s">
+      <c r="H10" s="65"/>
+      <c r="I10" s="65"/>
+      <c r="L10" s="117" t="s">
+        <v>184</v>
+      </c>
+      <c r="M10" s="65"/>
+      <c r="N10" s="65"/>
+      <c r="Q10" s="90" t="s">
+        <v>226</v>
+      </c>
+      <c r="R10" s="65"/>
+      <c r="S10" s="65"/>
+    </row>
+    <row r="11" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B11" s="123" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="G11" s="125" t="s">
+        <v>185</v>
+      </c>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="L11" s="58"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="65"/>
+      <c r="Q11" s="90" t="s">
+        <v>197</v>
+      </c>
+      <c r="R11" s="65"/>
+      <c r="S11" s="65"/>
+    </row>
+    <row r="12" spans="1:19" ht="58.5" x14ac:dyDescent="0.2">
+      <c r="B12" s="124" t="s">
+        <v>192</v>
+      </c>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="G12" s="125" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="64" t="s">
-        <v>92</v>
-      </c>
-      <c r="H6" s="64" t="s">
-        <v>93</v>
-      </c>
-      <c r="I6" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="L6" s="64" t="s">
-        <v>92</v>
-      </c>
-      <c r="M6" s="64" t="s">
-        <v>93</v>
-      </c>
-      <c r="N6" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q6" s="122" t="s">
-        <v>92</v>
-      </c>
-      <c r="R6" s="64" t="s">
-        <v>93</v>
-      </c>
-      <c r="S6" s="64" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B7" s="125" t="s">
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="65"/>
+      <c r="N12" s="65"/>
+      <c r="Q12" s="58"/>
+      <c r="R12" s="65"/>
+      <c r="S12" s="65"/>
+    </row>
+    <row r="14" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="K14" s="62" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="G15" s="63"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="L15" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="M15" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="G7" s="119" t="s">
-        <v>96</v>
-      </c>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="L7" s="119" t="s">
-        <v>97</v>
-      </c>
-      <c r="M7" s="66"/>
-      <c r="N7" s="66"/>
-      <c r="Q7" s="124" t="s">
-        <v>220</v>
-      </c>
-      <c r="R7" s="121"/>
-      <c r="S7" s="66"/>
-    </row>
-    <row r="8" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B8" s="125" t="s">
-        <v>207</v>
-      </c>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="G8" s="120" t="s">
-        <v>98</v>
-      </c>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
-      <c r="L8" s="119" t="s">
-        <v>197</v>
-      </c>
-      <c r="M8" s="66"/>
-      <c r="N8" s="66"/>
-      <c r="Q8" s="123" t="s">
-        <v>215</v>
-      </c>
-      <c r="R8" s="66"/>
-      <c r="S8" s="66"/>
-    </row>
-    <row r="9" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B9" s="125" t="s">
-        <v>208</v>
-      </c>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="G9" s="119" t="s">
-        <v>99</v>
-      </c>
-      <c r="H9" s="66"/>
-      <c r="I9" s="66"/>
-      <c r="L9" s="120" t="s">
-        <v>198</v>
-      </c>
-      <c r="M9" s="66"/>
-      <c r="N9" s="66"/>
-      <c r="Q9" s="91" t="s">
-        <v>216</v>
-      </c>
-      <c r="R9" s="66"/>
-      <c r="S9" s="66"/>
-    </row>
-    <row r="10" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B10" s="125" t="s">
-        <v>209</v>
-      </c>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="G10" s="119" t="s">
-        <v>100</v>
-      </c>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
-      <c r="L10" s="119" t="s">
-        <v>199</v>
-      </c>
-      <c r="M10" s="66"/>
-      <c r="N10" s="66"/>
-      <c r="Q10" s="91" t="s">
-        <v>217</v>
-      </c>
-      <c r="R10" s="66"/>
-      <c r="S10" s="66"/>
-    </row>
-    <row r="11" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B11" s="125" t="s">
-        <v>210</v>
-      </c>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="G11" s="127" t="s">
-        <v>200</v>
-      </c>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-      <c r="L11" s="58"/>
-      <c r="M11" s="66"/>
-      <c r="N11" s="66"/>
-      <c r="Q11" s="91" t="s">
-        <v>218</v>
-      </c>
-      <c r="R11" s="66"/>
-      <c r="S11" s="66"/>
-    </row>
-    <row r="12" spans="1:19" ht="58.5" x14ac:dyDescent="0.2">
-      <c r="B12" s="126" t="s">
-        <v>211</v>
-      </c>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="G12" s="127" t="s">
-        <v>101</v>
-      </c>
-      <c r="H12" s="66"/>
-      <c r="I12" s="66"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="66"/>
-      <c r="N12" s="66"/>
-      <c r="Q12" s="58"/>
-      <c r="R12" s="66"/>
-      <c r="S12" s="66"/>
-    </row>
-    <row r="14" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="62" t="s">
-        <v>206</v>
-      </c>
-      <c r="F14" s="62" t="s">
-        <v>102</v>
-      </c>
-      <c r="K14" s="62" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="G15" s="65" t="s">
-        <v>104</v>
-      </c>
-      <c r="H15" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="I15" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="L15" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="M15" s="64" t="s">
-        <v>105</v>
-      </c>
       <c r="N15" s="64" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="150" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G16" s="92" t="s">
-        <v>201</v>
-      </c>
-      <c r="H16" s="66"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="60" t="s">
-        <v>107</v>
-      </c>
-      <c r="L16" s="113" t="s">
-        <v>202</v>
-      </c>
-      <c r="M16" s="66"/>
-      <c r="N16" s="66"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G16" s="148"/>
+      <c r="L16" s="111" t="s">
+        <v>186</v>
+      </c>
+      <c r="M16" s="65"/>
+      <c r="N16" s="65"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4298,7 +4623,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14248B2F-CFC8-49A4-B9D9-36E17D955C3B}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -4320,10 +4645,10 @@
   <sheetData>
     <row r="2" spans="1:8" s="6" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
       <c r="D2" s="7" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="H2" s="13"/>
     </row>
@@ -4331,41 +4656,41 @@
       <c r="H3" s="13"/>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="155" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="155"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="152"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="152"/>
+      <c r="B4" s="172" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="172"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="169"/>
       <c r="H4" s="13"/>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="152"/>
-      <c r="C5" s="152"/>
-      <c r="D5" s="152"/>
-      <c r="E5" s="152"/>
-      <c r="F5" s="152"/>
-      <c r="G5" s="152"/>
+      <c r="B5" s="169"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="169"/>
       <c r="H5" s="13"/>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="152"/>
-      <c r="C6" s="152"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
+      <c r="B6" s="169"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="169"/>
+      <c r="F6" s="169"/>
+      <c r="G6" s="169"/>
       <c r="H6" s="13"/>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
+      <c r="B7" s="169"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="169"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="169"/>
+      <c r="G7" s="169"/>
       <c r="H7" s="13"/>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -4373,27 +4698,27 @@
       <c r="C8" s="16"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="9" customFormat="1" ht="105" customHeight="1" x14ac:dyDescent="0.25">
@@ -4402,19 +4727,19 @@
         <v>1</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="H11" s="14"/>
     </row>
@@ -4528,7 +4853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7284FCDC-4A20-44A8-9FA1-6AC7B3A3FFDD}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4561,14 +4886,14 @@
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="7" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="22" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="I2" s="22"/>
       <c r="J2" s="13"/>
@@ -4593,15 +4918,15 @@
     </row>
     <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
-      <c r="B4" s="156" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" s="157"/>
-      <c r="D4" s="157"/>
-      <c r="E4" s="157"/>
-      <c r="F4" s="157"/>
-      <c r="G4" s="157"/>
-      <c r="H4" s="158"/>
+      <c r="B4" s="173" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="174"/>
+      <c r="D4" s="174"/>
+      <c r="E4" s="174"/>
+      <c r="F4" s="174"/>
+      <c r="G4" s="174"/>
+      <c r="H4" s="175"/>
       <c r="I4" s="38"/>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
@@ -4610,13 +4935,13 @@
     </row>
     <row r="5" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
-      <c r="B5" s="159"/>
-      <c r="C5" s="152"/>
-      <c r="D5" s="152"/>
-      <c r="E5" s="152"/>
-      <c r="F5" s="152"/>
-      <c r="G5" s="152"/>
-      <c r="H5" s="160"/>
+      <c r="B5" s="176"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="169"/>
+      <c r="H5" s="177"/>
       <c r="I5" s="38"/>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
@@ -4625,13 +4950,13 @@
     </row>
     <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
-      <c r="B6" s="159"/>
-      <c r="C6" s="152"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="160"/>
+      <c r="B6" s="176"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="169"/>
+      <c r="F6" s="169"/>
+      <c r="G6" s="169"/>
+      <c r="H6" s="177"/>
       <c r="I6" s="38"/>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
@@ -4640,13 +4965,13 @@
     </row>
     <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
-      <c r="B7" s="161"/>
-      <c r="C7" s="162"/>
-      <c r="D7" s="162"/>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="162"/>
-      <c r="H7" s="163"/>
+      <c r="B7" s="178"/>
+      <c r="C7" s="179"/>
+      <c r="D7" s="179"/>
+      <c r="E7" s="179"/>
+      <c r="F7" s="179"/>
+      <c r="G7" s="179"/>
+      <c r="H7" s="180"/>
       <c r="I7" s="38"/>
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
@@ -4674,1176 +4999,1176 @@
       <c r="L9" s="12"/>
     </row>
     <row r="10" spans="1:13" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="B10" s="101" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="102" t="s">
-        <v>125</v>
-      </c>
-      <c r="D10" s="102" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" s="102" t="s">
-        <v>127</v>
-      </c>
-      <c r="F10" s="102" t="s">
-        <v>128</v>
-      </c>
-      <c r="G10" s="102" t="s">
-        <v>129</v>
-      </c>
-      <c r="H10" s="102" t="s">
-        <v>80</v>
-      </c>
-      <c r="I10" s="102" t="s">
-        <v>130</v>
-      </c>
-      <c r="J10" s="102" t="s">
-        <v>131</v>
-      </c>
-      <c r="K10" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="L10" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="M10" s="89" t="s">
-        <v>132</v>
+      <c r="B10" s="99" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="100" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="100" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" s="100" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" s="100" t="s">
+        <v>117</v>
+      </c>
+      <c r="G10" s="100" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" s="100" t="s">
+        <v>119</v>
+      </c>
+      <c r="J10" s="100" t="s">
+        <v>120</v>
+      </c>
+      <c r="K10" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="L10" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="M10" s="88" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
-      <c r="B11" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C11" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D11" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E11" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F11" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G11" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H11" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I11" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J11" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K11" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="L11" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="M11" s="89" t="s">
-        <v>132</v>
+      <c r="B11" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G11" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H11" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I11" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J11" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K11" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="L11" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="M11" s="88" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
-      <c r="B12" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D12" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E12" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G12" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H12" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I12" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J12" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K12" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="L12" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="M12" s="89" t="s">
-        <v>132</v>
+      <c r="B12" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F12" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G12" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H12" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J12" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K12" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="L12" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="M12" s="88" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C13" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D13" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E13" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F13" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G13" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H13" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I13" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J13" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K13" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="L13" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="M13" s="89" t="s">
-        <v>132</v>
+      <c r="B13" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G13" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J13" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K13" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="L13" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="M13" s="88" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C14" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D14" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E14" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F14" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G14" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H14" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I14" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J14" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K14" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="L14" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="M14" s="89" t="s">
-        <v>132</v>
+      <c r="B14" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D14" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G14" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H14" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J14" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K14" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="L14" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="M14" s="88" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B15" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C15" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E15" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F15" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G15" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H15" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I15" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J15" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K15" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="L15" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="M15" s="89" t="s">
-        <v>132</v>
+      <c r="B15" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G15" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H15" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I15" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J15" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K15" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="L15" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="M15" s="88" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B16" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C16" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D16" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E16" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F16" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G16" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H16" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I16" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J16" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K16" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="L16" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="M16" s="89" t="s">
-        <v>132</v>
+      <c r="B16" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D16" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G16" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I16" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J16" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K16" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="L16" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="M16" s="88" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B17" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C17" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D17" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E17" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F17" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G17" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H17" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I17" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J17" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K17" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="L17" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="M17" s="89" t="s">
-        <v>132</v>
+      <c r="B17" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I17" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J17" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K17" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="L17" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="M17" s="88" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B18" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C18" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D18" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E18" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F18" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G18" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H18" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I18" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J18" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K18" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="L18" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="M18" s="89" t="s">
-        <v>132</v>
+      <c r="B18" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F18" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G18" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H18" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I18" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K18" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="L18" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="M18" s="88" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B19" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C19" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D19" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E19" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F19" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G19" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H19" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I19" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J19" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K19" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="L19" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="M19" s="89" t="s">
-        <v>132</v>
+      <c r="B19" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G19" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H19" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I19" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J19" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K19" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="L19" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="M19" s="88" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B20" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D20" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E20" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F20" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G20" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H20" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I20" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J20" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K20" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="L20" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="M20" s="89" t="s">
-        <v>132</v>
+      <c r="B20" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F20" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H20" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I20" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J20" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K20" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="L20" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="M20" s="88" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B21" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C21" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D21" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E21" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F21" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G21" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H21" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I21" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J21" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K21" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="L21" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="M21" s="89" t="s">
-        <v>132</v>
+      <c r="B21" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G21" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H21" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I21" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J21" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K21" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="L21" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="M21" s="88" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B22" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D22" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E22" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F22" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G22" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H22" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I22" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J22" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K22" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="L22" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="M22" s="89" t="s">
-        <v>132</v>
+      <c r="B22" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G22" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H22" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I22" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J22" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K22" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="L22" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="M22" s="88" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="2:13" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="B25" s="97" t="s">
-        <v>133</v>
-      </c>
-      <c r="C25" s="98" t="s">
-        <v>134</v>
-      </c>
-      <c r="D25" s="98" t="s">
-        <v>135</v>
-      </c>
-      <c r="E25" s="98" t="s">
-        <v>136</v>
-      </c>
-      <c r="F25" s="98" t="s">
-        <v>137</v>
-      </c>
-      <c r="G25" s="98" t="s">
-        <v>138</v>
-      </c>
-      <c r="H25" s="98" t="s">
-        <v>139</v>
-      </c>
-      <c r="I25" s="98" t="s">
-        <v>140</v>
-      </c>
-      <c r="J25" s="98" t="s">
-        <v>80</v>
-      </c>
-      <c r="K25" s="98" t="s">
+      <c r="B25" s="95" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="96" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="96" t="s">
+        <v>124</v>
+      </c>
+      <c r="E25" s="96" t="s">
+        <v>125</v>
+      </c>
+      <c r="F25" s="96" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" s="96" t="s">
+        <v>127</v>
+      </c>
+      <c r="H25" s="96" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" s="96" t="s">
+        <v>129</v>
+      </c>
+      <c r="J25" s="96" t="s">
+        <v>78</v>
+      </c>
+      <c r="K25" s="96" t="s">
+        <v>119</v>
+      </c>
+      <c r="L25" s="96" t="s">
+        <v>120</v>
+      </c>
+      <c r="M25" s="106" t="s">
         <v>130</v>
       </c>
-      <c r="L25" s="98" t="s">
-        <v>131</v>
-      </c>
-      <c r="M25" s="108" t="s">
-        <v>141</v>
-      </c>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B26" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C26" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D26" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E26" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F26" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G26" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H26" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I26" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J26" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K26" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="L26" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="M26" s="100" t="s">
-        <v>132</v>
+      <c r="B26" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F26" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H26" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I26" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J26" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K26" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="L26" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="M26" s="98" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B27" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C27" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E27" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F27" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G27" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H27" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I27" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J27" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K27" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="L27" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="M27" s="100" t="s">
-        <v>132</v>
+      <c r="B27" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F27" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H27" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I27" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J27" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K27" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="L27" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="M27" s="98" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B28" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C28" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D28" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E28" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F28" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G28" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H28" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I28" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J28" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K28" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="L28" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="M28" s="100" t="s">
-        <v>132</v>
+      <c r="B28" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F28" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H28" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I28" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J28" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K28" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="L28" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="M28" s="98" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B29" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C29" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D29" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E29" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F29" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G29" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H29" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I29" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J29" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K29" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="L29" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="M29" s="100" t="s">
-        <v>132</v>
+      <c r="B29" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F29" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G29" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H29" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I29" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J29" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K29" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="L29" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="M29" s="98" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B30" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C30" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E30" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F30" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G30" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H30" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I30" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J30" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K30" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="L30" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="M30" s="100" t="s">
-        <v>132</v>
+      <c r="B30" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F30" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G30" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H30" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I30" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J30" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K30" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="L30" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="M30" s="98" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B31" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C31" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D31" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E31" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F31" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G31" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H31" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I31" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J31" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K31" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="L31" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="M31" s="100" t="s">
-        <v>132</v>
+      <c r="B31" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F31" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G31" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H31" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I31" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J31" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K31" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="L31" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="M31" s="98" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B32" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C32" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E32" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F32" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G32" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H32" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I32" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J32" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K32" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="L32" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="M32" s="100" t="s">
-        <v>132</v>
+      <c r="B32" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E32" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F32" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G32" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H32" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I32" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J32" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K32" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="L32" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="M32" s="98" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B33" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C33" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D33" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E33" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F33" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G33" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H33" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I33" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J33" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K33" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="L33" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="M33" s="100" t="s">
-        <v>132</v>
+      <c r="B33" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F33" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G33" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H33" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I33" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J33" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K33" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="L33" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="M33" s="98" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B34" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C34" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D34" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E34" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F34" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G34" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H34" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I34" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J34" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K34" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="L34" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="M34" s="100" t="s">
-        <v>132</v>
+      <c r="B34" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D34" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E34" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G34" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H34" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I34" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J34" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K34" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="L34" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="M34" s="98" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B35" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C35" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D35" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E35" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F35" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G35" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H35" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I35" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J35" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K35" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="L35" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="M35" s="100" t="s">
-        <v>132</v>
+      <c r="B35" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C35" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E35" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F35" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G35" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H35" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I35" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J35" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K35" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="L35" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="M35" s="98" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B36" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C36" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D36" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E36" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F36" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G36" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H36" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I36" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J36" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K36" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="L36" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="M36" s="100" t="s">
-        <v>132</v>
+      <c r="B36" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C36" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E36" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F36" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G36" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H36" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I36" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J36" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K36" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="L36" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="M36" s="98" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B37" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="C37" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D37" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="E37" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="F37" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="G37" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H37" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I37" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="J37" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="K37" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="L37" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="M37" s="100" t="s">
-        <v>132</v>
+      <c r="B37" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C37" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E37" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="F37" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="G37" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="H37" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="I37" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="J37" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="K37" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="L37" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="M37" s="98" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B40" s="105"/>
-      <c r="C40" s="105"/>
-      <c r="D40" s="105"/>
-      <c r="E40" s="105"/>
-      <c r="F40" s="105"/>
-      <c r="G40" s="105"/>
-      <c r="H40" s="105"/>
-      <c r="I40" s="105"/>
-      <c r="J40" s="105"/>
-      <c r="K40" s="105"/>
-      <c r="L40" s="105"/>
-      <c r="M40" s="106"/>
+      <c r="B40" s="103"/>
+      <c r="C40" s="103"/>
+      <c r="D40" s="103"/>
+      <c r="E40" s="103"/>
+      <c r="F40" s="103"/>
+      <c r="G40" s="103"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="103"/>
+      <c r="J40" s="103"/>
+      <c r="K40" s="103"/>
+      <c r="L40" s="103"/>
+      <c r="M40" s="104"/>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B41" s="107"/>
-      <c r="C41" s="107"/>
-      <c r="D41" s="107"/>
-      <c r="E41" s="107"/>
-      <c r="F41" s="107"/>
-      <c r="G41" s="107"/>
-      <c r="H41" s="107"/>
-      <c r="I41" s="107"/>
-      <c r="J41" s="107"/>
-      <c r="K41" s="107"/>
-      <c r="L41" s="107"/>
-      <c r="M41" s="107"/>
+      <c r="B41" s="105"/>
+      <c r="C41" s="105"/>
+      <c r="D41" s="105"/>
+      <c r="E41" s="105"/>
+      <c r="F41" s="105"/>
+      <c r="G41" s="105"/>
+      <c r="H41" s="105"/>
+      <c r="I41" s="105"/>
+      <c r="J41" s="105"/>
+      <c r="K41" s="105"/>
+      <c r="L41" s="105"/>
+      <c r="M41" s="105"/>
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B42" s="107"/>
-      <c r="C42" s="107"/>
-      <c r="D42" s="107"/>
-      <c r="E42" s="107"/>
-      <c r="F42" s="107"/>
-      <c r="G42" s="107"/>
-      <c r="H42" s="107"/>
-      <c r="I42" s="107"/>
-      <c r="J42" s="107"/>
-      <c r="K42" s="107"/>
-      <c r="L42" s="107"/>
-      <c r="M42" s="107"/>
+      <c r="B42" s="105"/>
+      <c r="C42" s="105"/>
+      <c r="D42" s="105"/>
+      <c r="E42" s="105"/>
+      <c r="F42" s="105"/>
+      <c r="G42" s="105"/>
+      <c r="H42" s="105"/>
+      <c r="I42" s="105"/>
+      <c r="J42" s="105"/>
+      <c r="K42" s="105"/>
+      <c r="L42" s="105"/>
+      <c r="M42" s="105"/>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B43" s="107"/>
-      <c r="C43" s="107"/>
-      <c r="D43" s="107"/>
-      <c r="E43" s="107"/>
-      <c r="F43" s="107"/>
-      <c r="G43" s="107"/>
-      <c r="H43" s="107"/>
-      <c r="I43" s="107"/>
-      <c r="J43" s="107"/>
-      <c r="K43" s="107"/>
-      <c r="L43" s="107"/>
-      <c r="M43" s="107"/>
+      <c r="B43" s="105"/>
+      <c r="C43" s="105"/>
+      <c r="D43" s="105"/>
+      <c r="E43" s="105"/>
+      <c r="F43" s="105"/>
+      <c r="G43" s="105"/>
+      <c r="H43" s="105"/>
+      <c r="I43" s="105"/>
+      <c r="J43" s="105"/>
+      <c r="K43" s="105"/>
+      <c r="L43" s="105"/>
+      <c r="M43" s="105"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B44" s="107"/>
-      <c r="C44" s="107"/>
-      <c r="D44" s="107"/>
-      <c r="E44" s="107"/>
-      <c r="F44" s="107"/>
-      <c r="G44" s="107"/>
-      <c r="H44" s="107"/>
-      <c r="I44" s="107"/>
-      <c r="J44" s="107"/>
-      <c r="K44" s="107"/>
-      <c r="L44" s="107"/>
-      <c r="M44" s="107"/>
+      <c r="B44" s="105"/>
+      <c r="C44" s="105"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="105"/>
+      <c r="F44" s="105"/>
+      <c r="G44" s="105"/>
+      <c r="H44" s="105"/>
+      <c r="I44" s="105"/>
+      <c r="J44" s="105"/>
+      <c r="K44" s="105"/>
+      <c r="L44" s="105"/>
+      <c r="M44" s="105"/>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B45" s="107"/>
-      <c r="C45" s="107"/>
-      <c r="D45" s="107"/>
-      <c r="E45" s="107"/>
-      <c r="F45" s="107"/>
-      <c r="G45" s="107"/>
-      <c r="H45" s="107"/>
-      <c r="I45" s="107"/>
-      <c r="J45" s="107"/>
-      <c r="K45" s="107"/>
-      <c r="L45" s="107"/>
-      <c r="M45" s="107"/>
+      <c r="B45" s="105"/>
+      <c r="C45" s="105"/>
+      <c r="D45" s="105"/>
+      <c r="E45" s="105"/>
+      <c r="F45" s="105"/>
+      <c r="G45" s="105"/>
+      <c r="H45" s="105"/>
+      <c r="I45" s="105"/>
+      <c r="J45" s="105"/>
+      <c r="K45" s="105"/>
+      <c r="L45" s="105"/>
+      <c r="M45" s="105"/>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B46" s="107"/>
-      <c r="C46" s="107"/>
-      <c r="D46" s="107"/>
-      <c r="E46" s="107"/>
-      <c r="F46" s="107"/>
-      <c r="G46" s="107"/>
-      <c r="H46" s="107"/>
-      <c r="I46" s="107"/>
-      <c r="J46" s="107"/>
-      <c r="K46" s="107"/>
-      <c r="L46" s="107"/>
-      <c r="M46" s="107"/>
+      <c r="B46" s="105"/>
+      <c r="C46" s="105"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="105"/>
+      <c r="F46" s="105"/>
+      <c r="G46" s="105"/>
+      <c r="H46" s="105"/>
+      <c r="I46" s="105"/>
+      <c r="J46" s="105"/>
+      <c r="K46" s="105"/>
+      <c r="L46" s="105"/>
+      <c r="M46" s="105"/>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B47" s="107"/>
-      <c r="C47" s="107"/>
-      <c r="D47" s="107"/>
-      <c r="E47" s="107"/>
-      <c r="F47" s="107"/>
-      <c r="G47" s="107"/>
-      <c r="H47" s="107"/>
-      <c r="I47" s="107"/>
-      <c r="J47" s="107"/>
-      <c r="K47" s="107"/>
-      <c r="L47" s="107"/>
-      <c r="M47" s="107"/>
+      <c r="B47" s="105"/>
+      <c r="C47" s="105"/>
+      <c r="D47" s="105"/>
+      <c r="E47" s="105"/>
+      <c r="F47" s="105"/>
+      <c r="G47" s="105"/>
+      <c r="H47" s="105"/>
+      <c r="I47" s="105"/>
+      <c r="J47" s="105"/>
+      <c r="K47" s="105"/>
+      <c r="L47" s="105"/>
+      <c r="M47" s="105"/>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B48" s="107"/>
-      <c r="C48" s="107"/>
-      <c r="D48" s="107"/>
-      <c r="E48" s="107"/>
-      <c r="F48" s="107"/>
-      <c r="G48" s="107"/>
-      <c r="H48" s="107"/>
-      <c r="I48" s="107"/>
-      <c r="J48" s="107"/>
-      <c r="K48" s="107"/>
-      <c r="L48" s="107"/>
-      <c r="M48" s="107"/>
+      <c r="B48" s="105"/>
+      <c r="C48" s="105"/>
+      <c r="D48" s="105"/>
+      <c r="E48" s="105"/>
+      <c r="F48" s="105"/>
+      <c r="G48" s="105"/>
+      <c r="H48" s="105"/>
+      <c r="I48" s="105"/>
+      <c r="J48" s="105"/>
+      <c r="K48" s="105"/>
+      <c r="L48" s="105"/>
+      <c r="M48" s="105"/>
     </row>
     <row r="49" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B49" s="107"/>
-      <c r="C49" s="107"/>
-      <c r="D49" s="107"/>
-      <c r="E49" s="107"/>
-      <c r="F49" s="107"/>
-      <c r="G49" s="107"/>
-      <c r="H49" s="107"/>
-      <c r="I49" s="107"/>
-      <c r="J49" s="107"/>
-      <c r="K49" s="107"/>
-      <c r="L49" s="107"/>
-      <c r="M49" s="107"/>
+      <c r="B49" s="105"/>
+      <c r="C49" s="105"/>
+      <c r="D49" s="105"/>
+      <c r="E49" s="105"/>
+      <c r="F49" s="105"/>
+      <c r="G49" s="105"/>
+      <c r="H49" s="105"/>
+      <c r="I49" s="105"/>
+      <c r="J49" s="105"/>
+      <c r="K49" s="105"/>
+      <c r="L49" s="105"/>
+      <c r="M49" s="105"/>
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B50" s="107"/>
-      <c r="C50" s="107"/>
-      <c r="D50" s="107"/>
-      <c r="E50" s="107"/>
-      <c r="F50" s="107"/>
-      <c r="G50" s="107"/>
-      <c r="H50" s="107"/>
-      <c r="I50" s="107"/>
-      <c r="J50" s="107"/>
-      <c r="K50" s="107"/>
-      <c r="L50" s="107"/>
-      <c r="M50" s="107"/>
+      <c r="B50" s="105"/>
+      <c r="C50" s="105"/>
+      <c r="D50" s="105"/>
+      <c r="E50" s="105"/>
+      <c r="F50" s="105"/>
+      <c r="G50" s="105"/>
+      <c r="H50" s="105"/>
+      <c r="I50" s="105"/>
+      <c r="J50" s="105"/>
+      <c r="K50" s="105"/>
+      <c r="L50" s="105"/>
+      <c r="M50" s="105"/>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B51" s="107"/>
-      <c r="C51" s="107"/>
-      <c r="D51" s="107"/>
-      <c r="E51" s="107"/>
-      <c r="F51" s="107"/>
-      <c r="G51" s="107"/>
-      <c r="H51" s="107"/>
-      <c r="I51" s="107"/>
-      <c r="J51" s="107"/>
-      <c r="K51" s="107"/>
-      <c r="L51" s="107"/>
-      <c r="M51" s="107"/>
+      <c r="B51" s="105"/>
+      <c r="C51" s="105"/>
+      <c r="D51" s="105"/>
+      <c r="E51" s="105"/>
+      <c r="F51" s="105"/>
+      <c r="G51" s="105"/>
+      <c r="H51" s="105"/>
+      <c r="I51" s="105"/>
+      <c r="J51" s="105"/>
+      <c r="K51" s="105"/>
+      <c r="L51" s="105"/>
+      <c r="M51" s="105"/>
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B52" s="107"/>
-      <c r="C52" s="107"/>
-      <c r="D52" s="107"/>
-      <c r="E52" s="107"/>
-      <c r="F52" s="107"/>
-      <c r="G52" s="107"/>
-      <c r="H52" s="107"/>
-      <c r="I52" s="107"/>
-      <c r="J52" s="107"/>
-      <c r="K52" s="107"/>
-      <c r="L52" s="107"/>
-      <c r="M52" s="107"/>
+      <c r="B52" s="105"/>
+      <c r="C52" s="105"/>
+      <c r="D52" s="105"/>
+      <c r="E52" s="105"/>
+      <c r="F52" s="105"/>
+      <c r="G52" s="105"/>
+      <c r="H52" s="105"/>
+      <c r="I52" s="105"/>
+      <c r="J52" s="105"/>
+      <c r="K52" s="105"/>
+      <c r="L52" s="105"/>
+      <c r="M52" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5878,7 +6203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -5897,12 +6222,12 @@
     <col min="8" max="8" width="53.140625" style="16" customWidth="1"/>
     <col min="9" max="9" width="38.7109375" style="16" customWidth="1"/>
     <col min="10" max="10" width="26" style="16" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" style="138" customWidth="1"/>
-    <col min="12" max="12" width="22.28515625" style="138" customWidth="1"/>
-    <col min="13" max="13" width="25.28515625" style="138" customWidth="1"/>
-    <col min="14" max="14" width="20.28515625" style="138" customWidth="1"/>
-    <col min="15" max="15" width="25" style="138" customWidth="1"/>
-    <col min="16" max="16" width="17.28515625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" style="136" customWidth="1"/>
+    <col min="12" max="12" width="22.28515625" style="136" customWidth="1"/>
+    <col min="13" max="13" width="25.28515625" style="136" customWidth="1"/>
+    <col min="14" max="14" width="20.28515625" style="136" customWidth="1"/>
+    <col min="15" max="15" width="25" style="136" customWidth="1"/>
+    <col min="16" max="16" width="17.28515625" style="136" customWidth="1"/>
     <col min="17" max="17" width="21.5703125" style="16" customWidth="1"/>
     <col min="18" max="18" width="21.28515625" style="16" customWidth="1"/>
     <col min="19" max="19" width="26" style="16" customWidth="1"/>
@@ -5914,14 +6239,14 @@
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="7" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
-      <c r="I2" s="139" t="s">
-        <v>109</v>
+      <c r="I2" s="137" t="s">
+        <v>98</v>
       </c>
       <c r="J2" s="7"/>
       <c r="K2" s="13"/>
@@ -5949,17 +6274,17 @@
       <c r="P3" s="13"/>
     </row>
     <row r="4" spans="1:20" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="164" t="s">
-        <v>142</v>
-      </c>
-      <c r="C4" s="164"/>
-      <c r="D4" s="165"/>
-      <c r="E4" s="165"/>
-      <c r="F4" s="165"/>
-      <c r="G4" s="165"/>
-      <c r="H4" s="165"/>
-      <c r="I4" s="165"/>
-      <c r="J4" s="165"/>
+      <c r="B4" s="181" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="181"/>
+      <c r="D4" s="182"/>
+      <c r="E4" s="182"/>
+      <c r="F4" s="182"/>
+      <c r="G4" s="182"/>
+      <c r="H4" s="182"/>
+      <c r="I4" s="182"/>
+      <c r="J4" s="182"/>
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
@@ -5968,15 +6293,15 @@
       <c r="P4" s="13"/>
     </row>
     <row r="5" spans="1:20" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="165"/>
-      <c r="C5" s="165"/>
-      <c r="D5" s="165"/>
-      <c r="E5" s="165"/>
-      <c r="F5" s="165"/>
-      <c r="G5" s="165"/>
-      <c r="H5" s="165"/>
-      <c r="I5" s="165"/>
-      <c r="J5" s="165"/>
+      <c r="B5" s="182"/>
+      <c r="C5" s="182"/>
+      <c r="D5" s="182"/>
+      <c r="E5" s="182"/>
+      <c r="F5" s="182"/>
+      <c r="G5" s="182"/>
+      <c r="H5" s="182"/>
+      <c r="I5" s="182"/>
+      <c r="J5" s="182"/>
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
       <c r="M5" s="13"/>
@@ -5985,15 +6310,15 @@
       <c r="P5" s="13"/>
     </row>
     <row r="6" spans="1:20" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="165"/>
-      <c r="C6" s="165"/>
-      <c r="D6" s="165"/>
-      <c r="E6" s="165"/>
-      <c r="F6" s="165"/>
-      <c r="G6" s="165"/>
-      <c r="H6" s="165"/>
-      <c r="I6" s="165"/>
-      <c r="J6" s="165"/>
+      <c r="B6" s="182"/>
+      <c r="C6" s="182"/>
+      <c r="D6" s="182"/>
+      <c r="E6" s="182"/>
+      <c r="F6" s="182"/>
+      <c r="G6" s="182"/>
+      <c r="H6" s="182"/>
+      <c r="I6" s="182"/>
+      <c r="J6" s="182"/>
       <c r="K6" s="13"/>
       <c r="L6" s="13"/>
       <c r="M6" s="13"/>
@@ -6002,15 +6327,15 @@
       <c r="P6" s="13"/>
     </row>
     <row r="7" spans="1:20" s="6" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="165"/>
-      <c r="C7" s="165"/>
-      <c r="D7" s="165"/>
-      <c r="E7" s="165"/>
-      <c r="F7" s="165"/>
-      <c r="G7" s="165"/>
-      <c r="H7" s="165"/>
-      <c r="I7" s="165"/>
-      <c r="J7" s="165"/>
+      <c r="B7" s="182"/>
+      <c r="C7" s="182"/>
+      <c r="D7" s="182"/>
+      <c r="E7" s="182"/>
+      <c r="F7" s="182"/>
+      <c r="G7" s="182"/>
+      <c r="H7" s="182"/>
+      <c r="I7" s="182"/>
+      <c r="J7" s="182"/>
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
       <c r="M7" s="13"/>
@@ -6019,14 +6344,14 @@
       <c r="P7" s="13"/>
     </row>
     <row r="8" spans="1:20" s="6" customFormat="1" ht="121.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="166" t="s">
-        <v>224</v>
-      </c>
-      <c r="C8" s="167"/>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="167"/>
+      <c r="B8" s="183" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8" s="184"/>
+      <c r="D8" s="184"/>
+      <c r="E8" s="184"/>
+      <c r="F8" s="184"/>
+      <c r="G8" s="184"/>
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
       <c r="M8" s="13"/>
@@ -6035,385 +6360,385 @@
       <c r="P8" s="13"/>
     </row>
     <row r="10" spans="1:20" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="141" t="s">
+      <c r="B10" s="139" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="139" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" s="139" t="s">
+        <v>133</v>
+      </c>
+      <c r="E10" s="139" t="s">
+        <v>134</v>
+      </c>
+      <c r="F10" s="139" t="s">
+        <v>135</v>
+      </c>
+      <c r="G10" s="139" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="139" t="s">
+        <v>137</v>
+      </c>
+      <c r="I10" s="139" t="s">
+        <v>138</v>
+      </c>
+      <c r="J10" s="139" t="s">
+        <v>139</v>
+      </c>
+      <c r="K10" s="139" t="s">
+        <v>140</v>
+      </c>
+      <c r="L10" s="139" t="s">
+        <v>78</v>
+      </c>
+      <c r="M10" s="139" t="s">
+        <v>141</v>
+      </c>
+      <c r="N10" s="139" t="s">
+        <v>78</v>
+      </c>
+      <c r="O10" s="139" t="s">
+        <v>142</v>
+      </c>
+      <c r="P10" s="139" t="s">
         <v>143</v>
       </c>
-      <c r="C10" s="141" t="s">
-        <v>225</v>
-      </c>
-      <c r="D10" s="141" t="s">
+      <c r="Q10" s="140" t="s">
+        <v>80</v>
+      </c>
+      <c r="R10" s="141" t="s">
         <v>144</v>
       </c>
-      <c r="E10" s="141" t="s">
+      <c r="S10" s="141" t="s">
         <v>145</v>
       </c>
-      <c r="F10" s="141" t="s">
+      <c r="T10" s="141" t="s">
         <v>146</v>
       </c>
-      <c r="G10" s="141" t="s">
+    </row>
+    <row r="11" spans="1:20" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="138">
+        <v>1</v>
+      </c>
+      <c r="C11" s="138"/>
+      <c r="D11" s="138"/>
+      <c r="E11" s="138"/>
+      <c r="F11" s="138"/>
+      <c r="G11" s="138"/>
+      <c r="H11" s="138"/>
+      <c r="I11" s="138"/>
+      <c r="J11" s="138"/>
+      <c r="K11" s="138"/>
+      <c r="L11" s="138"/>
+      <c r="M11" s="138"/>
+      <c r="N11" s="138"/>
+      <c r="O11" s="138"/>
+      <c r="P11" s="138"/>
+      <c r="Q11" s="138"/>
+      <c r="R11" s="128" t="s">
         <v>147</v>
       </c>
-      <c r="H10" s="141" t="s">
+      <c r="S11" s="145"/>
+      <c r="T11" s="145"/>
+    </row>
+    <row r="12" spans="1:20" s="130" customFormat="1" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="127"/>
+      <c r="B12" s="129">
+        <v>2</v>
+      </c>
+      <c r="C12" s="129"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="142"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="142"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="143"/>
+      <c r="L12" s="144"/>
+      <c r="M12" s="129"/>
+      <c r="N12" s="144"/>
+      <c r="O12" s="144"/>
+      <c r="P12" s="144"/>
+      <c r="Q12" s="144"/>
+      <c r="R12" s="128" t="s">
+        <v>147</v>
+      </c>
+      <c r="S12" s="129" t="s">
         <v>148</v>
       </c>
-      <c r="I10" s="141" t="s">
+      <c r="T12" s="129" t="s">
         <v>149</v>
       </c>
-      <c r="J10" s="141" t="s">
-        <v>150</v>
-      </c>
-      <c r="K10" s="141" t="s">
-        <v>151</v>
-      </c>
-      <c r="L10" s="141" t="s">
-        <v>80</v>
-      </c>
-      <c r="M10" s="141" t="s">
-        <v>152</v>
-      </c>
-      <c r="N10" s="141" t="s">
-        <v>80</v>
-      </c>
-      <c r="O10" s="141" t="s">
-        <v>153</v>
-      </c>
-      <c r="P10" s="141" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q10" s="142" t="s">
-        <v>82</v>
-      </c>
-      <c r="R10" s="143" t="s">
-        <v>155</v>
-      </c>
-      <c r="S10" s="143" t="s">
-        <v>156</v>
-      </c>
-      <c r="T10" s="143" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="102" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="140">
-        <v>1</v>
-      </c>
-      <c r="C11" s="140"/>
-      <c r="D11" s="140"/>
-      <c r="E11" s="140"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="140"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="140"/>
-      <c r="L11" s="140"/>
-      <c r="M11" s="140"/>
-      <c r="N11" s="140"/>
-      <c r="O11" s="140"/>
-      <c r="P11" s="140"/>
-      <c r="Q11" s="140"/>
-      <c r="R11" s="130" t="s">
-        <v>158</v>
-      </c>
-      <c r="S11" s="147"/>
-      <c r="T11" s="147"/>
-    </row>
-    <row r="12" spans="1:20" s="132" customFormat="1" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="129"/>
-      <c r="B12" s="131">
-        <v>2</v>
-      </c>
-      <c r="C12" s="131"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="144"/>
-      <c r="F12" s="144"/>
-      <c r="G12" s="144"/>
-      <c r="H12" s="144"/>
-      <c r="I12" s="144"/>
-      <c r="J12" s="144"/>
-      <c r="K12" s="145"/>
-      <c r="L12" s="146"/>
-      <c r="M12" s="131"/>
-      <c r="N12" s="146"/>
-      <c r="O12" s="146"/>
-      <c r="P12" s="146"/>
-      <c r="Q12" s="146"/>
-      <c r="R12" s="130" t="s">
-        <v>158</v>
-      </c>
-      <c r="S12" s="131" t="s">
-        <v>159</v>
-      </c>
-      <c r="T12" s="131" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D13" s="133"/>
-      <c r="E13" s="133"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="133"/>
-      <c r="H13" s="133"/>
-      <c r="I13" s="133"/>
-      <c r="K13" s="134"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="135"/>
-      <c r="Q13" s="136"/>
-    </row>
-    <row r="14" spans="1:20" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D14" s="133"/>
-      <c r="E14" s="133"/>
-      <c r="F14" s="133"/>
-      <c r="G14" s="133"/>
-      <c r="H14" s="133"/>
-      <c r="I14" s="133"/>
-      <c r="K14" s="134"/>
-      <c r="L14" s="135"/>
-      <c r="M14" s="135"/>
-      <c r="N14" s="135"/>
-      <c r="O14" s="135"/>
-      <c r="P14" s="135"/>
-      <c r="Q14" s="136"/>
-    </row>
-    <row r="15" spans="1:20" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D15" s="133"/>
-      <c r="E15" s="133"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="133"/>
-      <c r="I15" s="133"/>
-      <c r="K15" s="134"/>
-      <c r="L15" s="135"/>
-      <c r="M15" s="135"/>
-      <c r="N15" s="135"/>
-      <c r="O15" s="135"/>
-      <c r="P15" s="135"/>
-      <c r="Q15" s="137"/>
-    </row>
-    <row r="16" spans="1:20" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D16" s="133"/>
-      <c r="E16" s="133"/>
-      <c r="F16" s="133"/>
-      <c r="G16" s="133"/>
-      <c r="H16" s="133"/>
-      <c r="I16" s="133"/>
-      <c r="K16" s="134"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="135"/>
-      <c r="P16" s="135"/>
-      <c r="Q16" s="137"/>
-    </row>
-    <row r="17" spans="4:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D17" s="133"/>
-      <c r="E17" s="133"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="133"/>
-      <c r="H17" s="133"/>
-      <c r="I17" s="133"/>
-      <c r="K17" s="134"/>
-      <c r="L17" s="135"/>
-      <c r="M17" s="135"/>
-      <c r="N17" s="135"/>
-      <c r="O17" s="135"/>
-      <c r="P17" s="135"/>
-      <c r="Q17" s="137"/>
-    </row>
-    <row r="18" spans="4:17" s="132" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="133"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="133"/>
-      <c r="G18" s="133"/>
-      <c r="H18" s="133"/>
-      <c r="I18" s="133"/>
-      <c r="K18" s="134"/>
-      <c r="L18" s="135"/>
-      <c r="M18" s="135"/>
-      <c r="N18" s="135"/>
-      <c r="O18" s="135"/>
-      <c r="P18" s="135"/>
-      <c r="Q18" s="137"/>
-    </row>
-    <row r="19" spans="4:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="133"/>
-      <c r="I19" s="133"/>
-      <c r="K19" s="134"/>
-      <c r="L19" s="135"/>
-      <c r="M19" s="135"/>
-      <c r="N19" s="135"/>
-      <c r="O19" s="135"/>
-      <c r="P19" s="135"/>
-      <c r="Q19" s="137"/>
-    </row>
-    <row r="20" spans="4:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K20" s="135"/>
-      <c r="L20" s="135"/>
-      <c r="M20" s="135"/>
-      <c r="N20" s="135"/>
-      <c r="O20" s="135"/>
-      <c r="P20" s="135"/>
-      <c r="Q20" s="136"/>
-    </row>
-    <row r="21" spans="4:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K21" s="135"/>
-      <c r="L21" s="135"/>
-      <c r="M21" s="135"/>
-      <c r="N21" s="135"/>
-      <c r="O21" s="135"/>
-      <c r="P21" s="135"/>
-      <c r="Q21" s="136"/>
-    </row>
-    <row r="22" spans="4:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K22" s="135"/>
-      <c r="L22" s="135"/>
-      <c r="M22" s="135"/>
-      <c r="N22" s="135"/>
-      <c r="O22" s="135"/>
-      <c r="P22" s="135"/>
-      <c r="Q22" s="136"/>
-    </row>
-    <row r="23" spans="4:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K23" s="135"/>
-      <c r="L23" s="135"/>
-      <c r="M23" s="135"/>
-      <c r="N23" s="135"/>
-      <c r="O23" s="135"/>
-      <c r="P23" s="135"/>
-      <c r="Q23" s="136"/>
-    </row>
-    <row r="24" spans="4:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K24" s="135"/>
-      <c r="L24" s="135"/>
-      <c r="M24" s="135"/>
-      <c r="N24" s="135"/>
-      <c r="O24" s="135"/>
-      <c r="P24" s="135"/>
-      <c r="Q24" s="136"/>
-    </row>
-    <row r="25" spans="4:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K25" s="135"/>
-      <c r="L25" s="135"/>
-      <c r="M25" s="135"/>
-      <c r="N25" s="135"/>
-      <c r="O25" s="135"/>
-      <c r="P25" s="135"/>
-      <c r="Q25" s="136"/>
-    </row>
-    <row r="26" spans="4:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K26" s="135"/>
-      <c r="L26" s="135"/>
-      <c r="M26" s="135"/>
-      <c r="N26" s="135"/>
-      <c r="O26" s="135"/>
-      <c r="P26" s="135"/>
-      <c r="Q26" s="136"/>
-    </row>
-    <row r="27" spans="4:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K27" s="135"/>
-      <c r="L27" s="135"/>
-      <c r="M27" s="135"/>
-      <c r="N27" s="135"/>
-      <c r="O27" s="135"/>
-      <c r="P27" s="135"/>
-      <c r="Q27" s="136"/>
-    </row>
-    <row r="28" spans="4:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K28" s="135"/>
-      <c r="L28" s="135"/>
-      <c r="M28" s="135"/>
-      <c r="N28" s="135"/>
-      <c r="O28" s="135"/>
-      <c r="P28" s="135"/>
-      <c r="Q28" s="136"/>
-    </row>
-    <row r="29" spans="4:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K29" s="135"/>
-      <c r="L29" s="135"/>
-      <c r="M29" s="135"/>
-      <c r="N29" s="135"/>
-      <c r="O29" s="135"/>
-      <c r="P29" s="135"/>
-      <c r="Q29" s="136"/>
-    </row>
-    <row r="30" spans="4:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K30" s="135"/>
-      <c r="L30" s="135"/>
-      <c r="M30" s="135"/>
-      <c r="N30" s="135"/>
-      <c r="O30" s="135"/>
-      <c r="P30" s="135"/>
-      <c r="Q30" s="136"/>
-    </row>
-    <row r="31" spans="4:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K31" s="135"/>
-      <c r="L31" s="135"/>
-      <c r="M31" s="135"/>
-      <c r="N31" s="135"/>
-      <c r="O31" s="135"/>
-      <c r="P31" s="135"/>
-      <c r="Q31" s="136"/>
-    </row>
-    <row r="32" spans="4:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K32" s="135"/>
-      <c r="L32" s="135"/>
-      <c r="M32" s="135"/>
-      <c r="N32" s="135"/>
-      <c r="O32" s="135"/>
-      <c r="P32" s="135"/>
-      <c r="Q32" s="136"/>
-    </row>
-    <row r="33" spans="11:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K33" s="135"/>
-      <c r="L33" s="135"/>
-      <c r="M33" s="135"/>
-      <c r="N33" s="135"/>
-      <c r="O33" s="135"/>
-      <c r="P33" s="135"/>
-      <c r="Q33" s="136"/>
-    </row>
-    <row r="34" spans="11:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K34" s="135"/>
-      <c r="L34" s="135"/>
-      <c r="M34" s="135"/>
-      <c r="N34" s="135"/>
-      <c r="O34" s="135"/>
-      <c r="P34" s="135"/>
-      <c r="Q34" s="136"/>
-    </row>
-    <row r="35" spans="11:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K35" s="135"/>
-      <c r="L35" s="135"/>
-      <c r="M35" s="135"/>
-      <c r="N35" s="135"/>
-      <c r="O35" s="135"/>
-      <c r="P35" s="135"/>
-      <c r="Q35" s="136"/>
-    </row>
-    <row r="36" spans="11:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K36" s="135"/>
-      <c r="L36" s="135"/>
-      <c r="M36" s="135"/>
-      <c r="N36" s="135"/>
-      <c r="O36" s="135"/>
-      <c r="P36" s="135"/>
-      <c r="Q36" s="136"/>
-    </row>
-    <row r="37" spans="11:17" s="132" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K37" s="135"/>
-      <c r="L37" s="135"/>
-      <c r="M37" s="135"/>
-      <c r="N37" s="135"/>
-      <c r="O37" s="135"/>
-      <c r="P37" s="135"/>
-      <c r="Q37" s="136"/>
+    </row>
+    <row r="13" spans="1:20" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D13" s="131"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="131"/>
+      <c r="I13" s="131"/>
+      <c r="K13" s="132"/>
+      <c r="L13" s="133"/>
+      <c r="M13" s="133"/>
+      <c r="N13" s="133"/>
+      <c r="O13" s="133"/>
+      <c r="P13" s="133"/>
+      <c r="Q13" s="134"/>
+    </row>
+    <row r="14" spans="1:20" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D14" s="131"/>
+      <c r="E14" s="131"/>
+      <c r="F14" s="131"/>
+      <c r="G14" s="131"/>
+      <c r="H14" s="131"/>
+      <c r="I14" s="131"/>
+      <c r="K14" s="132"/>
+      <c r="L14" s="133"/>
+      <c r="M14" s="133"/>
+      <c r="N14" s="133"/>
+      <c r="O14" s="133"/>
+      <c r="P14" s="133"/>
+      <c r="Q14" s="134"/>
+    </row>
+    <row r="15" spans="1:20" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D15" s="131"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="131"/>
+      <c r="I15" s="131"/>
+      <c r="K15" s="132"/>
+      <c r="L15" s="133"/>
+      <c r="M15" s="133"/>
+      <c r="N15" s="133"/>
+      <c r="O15" s="133"/>
+      <c r="P15" s="133"/>
+      <c r="Q15" s="135"/>
+    </row>
+    <row r="16" spans="1:20" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D16" s="131"/>
+      <c r="E16" s="131"/>
+      <c r="F16" s="131"/>
+      <c r="G16" s="131"/>
+      <c r="H16" s="131"/>
+      <c r="I16" s="131"/>
+      <c r="K16" s="132"/>
+      <c r="L16" s="133"/>
+      <c r="M16" s="133"/>
+      <c r="N16" s="133"/>
+      <c r="O16" s="133"/>
+      <c r="P16" s="133"/>
+      <c r="Q16" s="135"/>
+    </row>
+    <row r="17" spans="4:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D17" s="131"/>
+      <c r="E17" s="131"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="131"/>
+      <c r="H17" s="131"/>
+      <c r="I17" s="131"/>
+      <c r="K17" s="132"/>
+      <c r="L17" s="133"/>
+      <c r="M17" s="133"/>
+      <c r="N17" s="133"/>
+      <c r="O17" s="133"/>
+      <c r="P17" s="133"/>
+      <c r="Q17" s="135"/>
+    </row>
+    <row r="18" spans="4:17" s="130" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D18" s="131"/>
+      <c r="E18" s="131"/>
+      <c r="F18" s="131"/>
+      <c r="G18" s="131"/>
+      <c r="H18" s="131"/>
+      <c r="I18" s="131"/>
+      <c r="K18" s="132"/>
+      <c r="L18" s="133"/>
+      <c r="M18" s="133"/>
+      <c r="N18" s="133"/>
+      <c r="O18" s="133"/>
+      <c r="P18" s="133"/>
+      <c r="Q18" s="135"/>
+    </row>
+    <row r="19" spans="4:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D19" s="131"/>
+      <c r="E19" s="131"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="131"/>
+      <c r="I19" s="131"/>
+      <c r="K19" s="132"/>
+      <c r="L19" s="133"/>
+      <c r="M19" s="133"/>
+      <c r="N19" s="133"/>
+      <c r="O19" s="133"/>
+      <c r="P19" s="133"/>
+      <c r="Q19" s="135"/>
+    </row>
+    <row r="20" spans="4:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K20" s="133"/>
+      <c r="L20" s="133"/>
+      <c r="M20" s="133"/>
+      <c r="N20" s="133"/>
+      <c r="O20" s="133"/>
+      <c r="P20" s="133"/>
+      <c r="Q20" s="134"/>
+    </row>
+    <row r="21" spans="4:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K21" s="133"/>
+      <c r="L21" s="133"/>
+      <c r="M21" s="133"/>
+      <c r="N21" s="133"/>
+      <c r="O21" s="133"/>
+      <c r="P21" s="133"/>
+      <c r="Q21" s="134"/>
+    </row>
+    <row r="22" spans="4:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K22" s="133"/>
+      <c r="L22" s="133"/>
+      <c r="M22" s="133"/>
+      <c r="N22" s="133"/>
+      <c r="O22" s="133"/>
+      <c r="P22" s="133"/>
+      <c r="Q22" s="134"/>
+    </row>
+    <row r="23" spans="4:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K23" s="133"/>
+      <c r="L23" s="133"/>
+      <c r="M23" s="133"/>
+      <c r="N23" s="133"/>
+      <c r="O23" s="133"/>
+      <c r="P23" s="133"/>
+      <c r="Q23" s="134"/>
+    </row>
+    <row r="24" spans="4:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K24" s="133"/>
+      <c r="L24" s="133"/>
+      <c r="M24" s="133"/>
+      <c r="N24" s="133"/>
+      <c r="O24" s="133"/>
+      <c r="P24" s="133"/>
+      <c r="Q24" s="134"/>
+    </row>
+    <row r="25" spans="4:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K25" s="133"/>
+      <c r="L25" s="133"/>
+      <c r="M25" s="133"/>
+      <c r="N25" s="133"/>
+      <c r="O25" s="133"/>
+      <c r="P25" s="133"/>
+      <c r="Q25" s="134"/>
+    </row>
+    <row r="26" spans="4:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K26" s="133"/>
+      <c r="L26" s="133"/>
+      <c r="M26" s="133"/>
+      <c r="N26" s="133"/>
+      <c r="O26" s="133"/>
+      <c r="P26" s="133"/>
+      <c r="Q26" s="134"/>
+    </row>
+    <row r="27" spans="4:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K27" s="133"/>
+      <c r="L27" s="133"/>
+      <c r="M27" s="133"/>
+      <c r="N27" s="133"/>
+      <c r="O27" s="133"/>
+      <c r="P27" s="133"/>
+      <c r="Q27" s="134"/>
+    </row>
+    <row r="28" spans="4:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K28" s="133"/>
+      <c r="L28" s="133"/>
+      <c r="M28" s="133"/>
+      <c r="N28" s="133"/>
+      <c r="O28" s="133"/>
+      <c r="P28" s="133"/>
+      <c r="Q28" s="134"/>
+    </row>
+    <row r="29" spans="4:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K29" s="133"/>
+      <c r="L29" s="133"/>
+      <c r="M29" s="133"/>
+      <c r="N29" s="133"/>
+      <c r="O29" s="133"/>
+      <c r="P29" s="133"/>
+      <c r="Q29" s="134"/>
+    </row>
+    <row r="30" spans="4:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K30" s="133"/>
+      <c r="L30" s="133"/>
+      <c r="M30" s="133"/>
+      <c r="N30" s="133"/>
+      <c r="O30" s="133"/>
+      <c r="P30" s="133"/>
+      <c r="Q30" s="134"/>
+    </row>
+    <row r="31" spans="4:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K31" s="133"/>
+      <c r="L31" s="133"/>
+      <c r="M31" s="133"/>
+      <c r="N31" s="133"/>
+      <c r="O31" s="133"/>
+      <c r="P31" s="133"/>
+      <c r="Q31" s="134"/>
+    </row>
+    <row r="32" spans="4:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K32" s="133"/>
+      <c r="L32" s="133"/>
+      <c r="M32" s="133"/>
+      <c r="N32" s="133"/>
+      <c r="O32" s="133"/>
+      <c r="P32" s="133"/>
+      <c r="Q32" s="134"/>
+    </row>
+    <row r="33" spans="11:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K33" s="133"/>
+      <c r="L33" s="133"/>
+      <c r="M33" s="133"/>
+      <c r="N33" s="133"/>
+      <c r="O33" s="133"/>
+      <c r="P33" s="133"/>
+      <c r="Q33" s="134"/>
+    </row>
+    <row r="34" spans="11:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K34" s="133"/>
+      <c r="L34" s="133"/>
+      <c r="M34" s="133"/>
+      <c r="N34" s="133"/>
+      <c r="O34" s="133"/>
+      <c r="P34" s="133"/>
+      <c r="Q34" s="134"/>
+    </row>
+    <row r="35" spans="11:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K35" s="133"/>
+      <c r="L35" s="133"/>
+      <c r="M35" s="133"/>
+      <c r="N35" s="133"/>
+      <c r="O35" s="133"/>
+      <c r="P35" s="133"/>
+      <c r="Q35" s="134"/>
+    </row>
+    <row r="36" spans="11:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K36" s="133"/>
+      <c r="L36" s="133"/>
+      <c r="M36" s="133"/>
+      <c r="N36" s="133"/>
+      <c r="O36" s="133"/>
+      <c r="P36" s="133"/>
+      <c r="Q36" s="134"/>
+    </row>
+    <row r="37" spans="11:17" s="130" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K37" s="133"/>
+      <c r="L37" s="133"/>
+      <c r="M37" s="133"/>
+      <c r="N37" s="133"/>
+      <c r="O37" s="133"/>
+      <c r="P37" s="133"/>
+      <c r="Q37" s="134"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6443,116 +6768,6 @@
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;K000000 OFFICIAL-FOR PUBLIC RELEASE</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="40.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="37.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="34.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="42.85546875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="168" t="s">
-        <v>226</v>
-      </c>
-      <c r="C2" s="95" t="s">
-        <v>158</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="F2" s="171" t="s">
-        <v>228</v>
-      </c>
-      <c r="G2" s="96" t="s">
-        <v>160</v>
-      </c>
-      <c r="H2" s="77" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="144.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="169"/>
-      <c r="C3" s="94" t="s">
-        <v>162</v>
-      </c>
-      <c r="D3" s="148" t="s">
-        <v>163</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="171"/>
-      <c r="G3" s="96" t="s">
-        <v>164</v>
-      </c>
-      <c r="H3" s="77" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="170"/>
-      <c r="C4" s="93" t="s">
-        <v>166</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="F4" s="171"/>
-      <c r="G4" s="96" t="s">
-        <v>159</v>
-      </c>
-      <c r="H4" s="77" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="F7" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="F2:F4"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;K000000 OFFICIAL-FOR PUBLIC RELEASE&amp;1#_x000D_</oddHeader>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;K000000 OFFICIAL-FOR PUBLIC RELEASE</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -6800,15 +7015,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e1cd103-0302-4a32-9a4b-e115c950d959">
@@ -6817,6 +7023,15 @@
     <TaxCatchAll xmlns="50b62f6a-6a2d-4510-bfe7-b1a3c00072e4" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6839,14 +7054,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D186559C-C381-484C-9B7A-F4466E79AE25}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D71C399E-D560-405D-A693-6A86DF1C82D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -6857,6 +7064,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D186559C-C381-484C-9B7A-F4466E79AE25}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{9ff2627b-e365-4c50-8f1e-0699f40c3c6e}" enabled="1" method="Privileged" siteId="{078807bf-ce82-4688-bce0-0d811684dc46}" contentBits="3" removed="0"/>
